--- a/outputs/evaluation/decision/v2/CF_M05/run_1/CF_M05_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_1/CF_M05_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -515,107 +515,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6768999999999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7287</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AWS manages multiple levels of security and offers tools to protect data and infrastructures, facilitating compliance with legal regulations and international standards.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Amazon Web Services (AWS)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6804</v>
       </c>
     </row>
   </sheetData>
